--- a/user_inputs/terms.xlsx
+++ b/user_inputs/terms.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">Term</t>
   </si>
@@ -74,6 +74,9 @@
     <t xml:space="preserve">Secondary Term</t>
   </si>
   <si>
+    <t xml:space="preserve">Smart Position</t>
+  </si>
+  <si>
     <t xml:space="preserve">resistance</t>
   </si>
   <si>
@@ -92,21 +95,6 @@
     <t xml:space="preserve">number</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">auto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">isp</t>
-  </si>
-  <si>
     <t xml:space="preserve">EIDP Terms Schema Template</t>
   </si>
   <si>
@@ -138,6 +126,12 @@
   </si>
   <si>
     <t xml:space="preserve">                - Smart Snap Type: auto | number | date | time | title. Auto-detects if blank.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                - Secondary Term: optional label to validate near the chosen value (sweeps up to page top).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                - Smart Position: optional 1-based index to pick the Nth value to the right (overrides scoring).</t>
   </si>
   <si>
     <t xml:space="preserve">                - Units/Range still apply for numeric detection.</t>
@@ -237,12 +231,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -435,201 +425,86 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="14.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="0" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="0" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="C2" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="N2" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="O2" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="P2" s="0" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>41</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <v>43</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q6" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -648,104 +523,114 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
+      <c r="A1" s="0" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>29</v>
+      <c r="A2" s="0" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
